--- a/glossary.xlsx
+++ b/glossary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/SystemDocumentation/github/uactechdoc/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2730F25D-26C7-404C-B6F3-7D1E77C0C46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7FCEA1-3E98-2449-ABA4-43BF03913242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{FD61D8A1-D7A7-6B4D-AB92-59721C5EF8F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="180">
   <si>
     <t>Topic</t>
   </si>
@@ -433,6 +433,150 @@
   <si>
     <t>A composite of multiple video sources (up to 4) into a single layered output with resizable, positioned boxes over a background. It’s ideal for picture-in-picture (PiP) layouts in live productions, such as news shows, conferences, or multi-camera streams. SuperSource excels for complex, preset-driven live layouts like news or conferences, while DVE offers flexibility for custom single-element effects or when stacking multiple keys.
 A SuperSource is itself a source</t>
+  </si>
+  <si>
+    <t>Barn Doors</t>
+  </si>
+  <si>
+    <t>Snoots, Snouts</t>
+  </si>
+  <si>
+    <t>Black hinged panels or shutters (which open and close like real barn doors) attached to the front of a lamp fixture to control the spread of the light beam. Also see Snoots (or Snouts) .</t>
+  </si>
+  <si>
+    <t>Scoop: See Flood,</t>
+  </si>
+  <si>
+    <t>Broad</t>
+  </si>
+  <si>
+    <t>A type of floodlight used to provide broadside flat lighting. When it has twin lamps, it is termed a double broad or broadside.</t>
+  </si>
+  <si>
+    <t>Century Stand</t>
+  </si>
+  <si>
+    <t>Upright, pole-like stand with clamps. It may be used to hold a gobo extra small lights etc</t>
+  </si>
+  <si>
+    <t>Junior</t>
+  </si>
+  <si>
+    <t>Deuce</t>
+  </si>
+  <si>
+    <t>Nickname for a 2-kW lamp. Also see Junior.</t>
+  </si>
+  <si>
+    <t>Dimmer Board</t>
+  </si>
+  <si>
+    <t>Houses the appropriate switches and controls for fading down and brightening lights or banks of lights.</t>
+  </si>
+  <si>
+    <t>Elbows</t>
+  </si>
+  <si>
+    <t>Special hooks used to keep cables off floors.</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>Small rectangular gobo. An even smaller gobo is termed a clip. Terminology is quite fluid here; a thin flag might be called a blade; a round one might be called a target or (if very small) a dot. A flag with a small hole is called an ear.</t>
+  </si>
+  <si>
+    <t>Flood</t>
+  </si>
+  <si>
+    <t>Floodlighting and spotlighting are the two basic types of lighting. The flood is designed to illuminate a broad expanse; it is also called a SCOOP.</t>
+  </si>
+  <si>
+    <t>Black screen, cloth, or sheet used to block off unwanted light reflections into the camera lens. Also applied to a built-in pattern projector for Lekolights</t>
+  </si>
+  <si>
+    <t>Inky</t>
+  </si>
+  <si>
+    <t>Baby spotlight usually mounted on the front of a camera to lend extra sparkle to a person's eyes and teeth. Originally this term was a contraction of "incandescent" (thus, a small incandescent spotlight), but it also is applied in current usage to a small spotlight using the newer quartz-iodine lamp.</t>
+  </si>
+  <si>
+    <t>A light not quite as bright as a senior, usually rated at one or two kilowatts.</t>
+  </si>
+  <si>
+    <t>Keg Light</t>
+  </si>
+  <si>
+    <t>Small spotlight in a housing that resembles a keg.</t>
+  </si>
+  <si>
+    <t>Klieg Light</t>
+  </si>
+  <si>
+    <t>A flood-spotlight (either way). (Trade name of Kliegl Bros. Lighting.)</t>
+  </si>
+  <si>
+    <t>Leko</t>
+  </si>
+  <si>
+    <t>Leko (Lekolite): Special spotlight shuttered to provide a desired pattern of light. (Trade name of Century Lighting, Inc.)</t>
+  </si>
+  <si>
+    <t>Luninaire</t>
+  </si>
+  <si>
+    <t>Light fixture with lamp. (General term.)</t>
+  </si>
+  <si>
+    <t>Reflectors</t>
+  </si>
+  <si>
+    <t>Brightly polished concave surfaces used behind a lamp to concentrate the light rays in one direction. The term is also applied to exterior sheets (up to about 6' X 6') used to reflect light into desired locations (such as shadow fill).</t>
+  </si>
+  <si>
+    <t>Rifle</t>
+  </si>
+  <si>
+    <t>Spotlight with a very small beam of light used to pinpoint a small detail.</t>
+  </si>
+  <si>
+    <t>Scoop</t>
+  </si>
+  <si>
+    <t>Snoot</t>
+  </si>
+  <si>
+    <t>Snoots (or Snouts): Hoods placed in front of lamp housings to limit the area illuminated.</t>
+  </si>
+  <si>
+    <t>Spiders</t>
+  </si>
+  <si>
+    <t>The points where cables converge for connection to the current main. They are so termed because they resemble a spider's web.</t>
+  </si>
+  <si>
+    <t>Spill</t>
+  </si>
+  <si>
+    <t>Term for excess light that falls in areas not intended</t>
+  </si>
+  <si>
+    <t>Spotlight</t>
+  </si>
+  <si>
+    <t>Highly concentrated beam of light.</t>
+  </si>
+  <si>
+    <t>Striplights</t>
+  </si>
+  <si>
+    <t>Lights arranged in strips for lighting backings, windows, and cycloramas ("cycs"). A cyclorama is a semicircular or U-shaped hanging for a background.</t>
+  </si>
+  <si>
+    <t>Teaser</t>
+  </si>
+  <si>
+    <t>Large, flat gobo used to block overhead back light from the camera lens</t>
   </si>
 </sst>
 </file>
@@ -510,8 +654,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:D60" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:D60" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:D84" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:D84" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
     <sortCondition ref="A2:A56"/>
     <sortCondition ref="B2:B56"/>
@@ -823,10 +967,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327B4C12-DB51-F04E-97D5-67343BD74C6D}">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="94.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1574,6 +1719,300 @@
       </c>
       <c r="D60" s="2" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/glossary.xlsx
+++ b/glossary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7FCEA1-3E98-2449-ABA4-43BF03913242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DC177A-AAC5-A246-9E9E-1180E16C9235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{FD61D8A1-D7A7-6B4D-AB92-59721C5EF8F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="279">
   <si>
     <t>Topic</t>
   </si>
@@ -101,21 +101,9 @@
     <t>Dimmer</t>
   </si>
   <si>
-    <t>: A device which regulates the power sent to a lighting instrument (typically incandescent) this allows the intensity of the instrument to be varied. Usually DMX controlled, but could be controlled via an analog or proprietary protocols.</t>
-  </si>
-  <si>
-    <t>DMX / DMX512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">: an industry standard lighting control protocol. A universe is a group of 512 addresses, numbered 1 through 512. See also RDM. </t>
-  </si>
-  <si>
     <t>Gel</t>
   </si>
   <si>
-    <t xml:space="preserve">: a coloured sheet of special plastic which is used to physically change the colour of a light. </t>
-  </si>
-  <si>
     <t>Gel Frame</t>
   </si>
   <si>
@@ -143,13 +131,7 @@
     <t>Par / Par Can</t>
   </si>
   <si>
-    <t>: a type of lighting instrument with a fixed beam width. Some of them look like paint cans. Generally used for washes.</t>
-  </si>
-  <si>
     <t>RDM / Remote Device Management</t>
-  </si>
-  <si>
-    <t>: This is a management protocol that can run over the same cables as DMX. It is a bi-directional protocol. It can be used to change the configuration of some lighting fixtures (such as our ETC fixtures) without having physical access to the fixture.</t>
   </si>
   <si>
     <t>Rotator</t>
@@ -492,9 +474,6 @@
     <t>Floodlighting and spotlighting are the two basic types of lighting. The flood is designed to illuminate a broad expanse; it is also called a SCOOP.</t>
   </si>
   <si>
-    <t>Black screen, cloth, or sheet used to block off unwanted light reflections into the camera lens. Also applied to a built-in pattern projector for Lekolights</t>
-  </si>
-  <si>
     <t>Inky</t>
   </si>
   <si>
@@ -577,6 +556,422 @@
   </si>
   <si>
     <t>Large, flat gobo used to block overhead back light from the camera lens</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The state of being able to see or be seen. The most important fundamental. If
+the audience can’t see, everything else the lighting designer does is a waste of time.
+Studies have shown that visibility affects our ability to understand spoken speech. This
+doesn’t mean the audience must see everything all the time, but they should be focused
+on what the story is telling us.</t>
+  </si>
+  <si>
+    <t>Visibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The strength or amount of light produced by a specific lamp source. It is not
+always about how ‘bright’ the light is, but how ‘dim’.</t>
+  </si>
+  <si>
+    <t>Intensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Where the light hits and from what angle. Careful consideration of these
+factors can determine the visibility of the actor, depth and detail of scenery, as well as
+other areas such as given circumstances and mood.</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The use of color is one of the most noticeable defining elements of any lighting
+design. For many designers, color is the most personal of elements, and often times not
+only defines the design, but the personal style of the designer.</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>– Any change in visibility, intensity, distribution, or color, as well as physical
+movement when using Moving Lights. Not as apparent as some of the others, this is still
+a very important element that has a significant effect on the lighting design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movement </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – When an object or performer moves in and out of light.</t>
+  </si>
+  <si>
+    <t>Apparent Movement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - When the light itself moves.</t>
+  </si>
+  <si>
+    <t>Actual Movement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – The trigger for an action to be carried out at a specific time, normally called by a
+stage manager. They can be necessary for a lighting change or effect, a sound effect, or
+some sort of stage or set movement/change.</t>
+  </si>
+  <si>
+    <t>Cue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – A document like an architectural blueprint used specifically by theatrical
+lighting designers to illustrate and communicate the lighting design to members of the
+crew and staff.</t>
+  </si>
+  <si>
+    <t>Lightplot</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – The range of frequencies of electromagnetic radiation.
+Includes all visible and invisible light, radio and television signals, x-rays and microwaves.</t>
+  </si>
+  <si>
+    <t>Electromagnetic Spectrum</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Lighting fixture that can be used to create a general "fill" of light and
+color evenly across the stage.</t>
+  </si>
+  <si>
+    <t>Wash Fixture</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Fixture with a hard-edged beam. These fixtures are best for creating a
+“special” or using light to mask off a small, precise area, and also are the fixtures to use if
+you want to project a pattern, or “gobo”.</t>
+  </si>
+  <si>
+    <t>Spot Fixture</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The most commonly known instrument. Follow spots are used to highlight
+and follow a single performer onstage. Spotlights are controlled by a spotlight operator
+(or Spot Op) who tracks actors around the stage. Follow spots require a certain amount
+of skill to operate smoothly. They typically have a variety of colors that can be inserted
+with the flip of a lever, as well as a gate, dowser, focus control, and an iris. Used to
+follow a lead talent on stage.</t>
+  </si>
+  <si>
+    <t>Follow Spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - A small, stenciled, circular disc used in lighting fixtures to create a
+projected image or pattern. The term Gobo is short for “Go Between Optics”, describing
+the location where it needs to be positioned in the light path of a lighting fixture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – The point at which light waves intersect after refraction or reflection.</t>
+  </si>
+  <si>
+    <t>Focal Point</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Pronounced freh-NEL - A Fresnel lens maintains the curvature and prescription
+of a large convex lens in a much thinner version. The curve of the lens is stepped back
+towards the flat side at regular intervals. This is less expensive to produce and allows
+more even heat distribution through the glass, protecting the lens from expansion and
+contraction. The trade-off is a fuzzier, softer field. Used often for top light, backlight, and
+general washes.</t>
+  </si>
+  <si>
+    <t>Fresnel</t>
+  </si>
+  <si>
+    <t>Cyclorama</t>
+  </si>
+  <si>
+    <t>Cyc Lights</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Light from the back of a performer or object. Often used to pull the subject
+away from the background, sculps and adds depth to the subject. In film this can be
+referred to a hair light.</t>
+  </si>
+  <si>
+    <t>Back Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Light from up above or at the height of the subject to help sculpt the body
+and add fill to the sides of the subject. In film this is referred to as fill light.</t>
+  </si>
+  <si>
+    <t>Side Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Light directly above the subject.</t>
+  </si>
+  <si>
+    <t>Top Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Light to the front of the subject.</t>
+  </si>
+  <si>
+    <t>Front Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - A method of lighting using a front light in conjunction with
+two side lights.</t>
+  </si>
+  <si>
+    <t>Three Point Lighting</t>
+  </si>
+  <si>
+    <t>– A method of lighting similar to Three Point Lighting using a front
+light, two side lights, and a backlight or using a front light, a fill light, a backlight, and w a
+background light that illuminates walls or other scenery around the subject.</t>
+  </si>
+  <si>
+    <t>Four Point Lighting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – This method is widely known and used by theatre professionals.
+It uses two front lights at a 45-degree angle of the subject, one side being a warm gel
+color and the other side being a cool gel color. This helps replicate a highlight and
+shadow contrast with lighting.</t>
+  </si>
+  <si>
+    <t>McCandless Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Generally, a system of rope lines, blocks (pulleys), counterweights and
+related devices within a theater that enables a stage crew to fly (hoist) quickly, quietly
+and safely components such as curtains, lights, scenery, stage effects and, sometimes,
+people. These systems can either be manually operated or motorized. Rigging can also be
+stationary, or dead hung, in the case of an overhead grid.</t>
+  </si>
+  <si>
+    <t>Stage Rigging</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Originally a vertical pipe in a seating box used for stage lights, but now used
+to indicate any side lighting position.</t>
+  </si>
+  <si>
+    <t>Box Boom</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - An elevated service platform from which many of the technical functions of
+a theater, such as lighting and sound, may be manipulated.</t>
+  </si>
+  <si>
+    <t>Catwalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The line set is the fundamental machine of a typical fly system. The function
+of a typical line set is to fly (raise and lower) a slender beam (typically a steel pipe) known
+as a batten by hoisting it with lift lines (typically synthetic rope or steel cable). By
+hanging scenery, lighting, or other equipment on a batten, they in turn may also be
+flown. A batten is said to be "flying in" when it is being lowered toward the stage, and
+"flying out" when it is being raised into the fly space. Battens may be just a few feet in
+length or may extend from one wing (side) of the stage to the other. A batten is
+suspended from above by at least two lift lines, but long battens may require six or more
+lift lines.</t>
+  </si>
+  <si>
+    <t>Line Sets</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The means by which an instrument is connected to a dimmer or patch panel.
+Numbered for reference.</t>
+  </si>
+  <si>
+    <t>Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Method of flying scenery which uses a cradle containing
+weights to counterbalance the weight of flown scenery.</t>
+  </si>
+  <si>
+    <t>Counterweight System</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Part of the load in a counterweight system representing the weight of the
+empty batten; pipe weight should be left on the arbor when the load and its
+counterweight is removed.</t>
+  </si>
+  <si>
+    <t>Pipe Weight</t>
+  </si>
+  <si>
+    <t>Dimmer Rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The room backstage which contains the dimmer racks which power the
+lighting rig in the theatre.</t>
+  </si>
+  <si>
+    <t>Dimmer Room</t>
+  </si>
+  <si>
+    <t>DMX</t>
+  </si>
+  <si>
+    <t>DMX Universe</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - An electronic device used in theatrical lighting design to control
+multiple lights at once, also known as a Light Board.</t>
+  </si>
+  <si>
+    <t>Lighting Console</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Ellipsoidal reflector spotlights do a lot and can be very precise. They can
+accept gobos and irises and have built-in shutters for shaping the field of light.
+Ellipsoidals require a degree of maintenance and finesse; they are less easy to use than
+other types of instruments and are a bit more expensive. Used often for front light or side
+light in dance.</t>
+  </si>
+  <si>
+    <t>Ellipsoidal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - An ellipsoidal reflector spotlight (ERS) used in stage lighting.</t>
+  </si>
+  <si>
+    <t>Source Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Fixed at two points to the sides of the instrument, providing an axis of rotation.
+The base of the yoke is typically a single bolt around which the yoke can be rotated,
+providing a second axis of rotation. Combined together, these two axes allow the fixture
+to point nearly anywhere in a spherical range of motion encircling the yoke.</t>
+  </si>
+  <si>
+    <t>Yoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Cable or chain to be attached between the fixture and its truss. Lighting
+fixtures often are suspended very high above performers heads and could cause serious
+injury or death if they fell by accident or due to incorrect attachment. The safety cable
+would halt the fall of the fixture before it could cause serious damage or injury.</t>
+  </si>
+  <si>
+    <t>Safety Cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – A preliminary or advance focus. If you know where the light will be focused,
+point it in that general directions to make sure it is tight, and the cable will reach.
+Accessory Slot – On a Source Four, can hold multiple accessories for the light such as
+templates or template rotators.</t>
+  </si>
+  <si>
+    <t>Pre-focus</t>
+  </si>
+  <si>
+    <t>Gel or Light Filter</t>
+  </si>
+  <si>
+    <t>Gobo or Template</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - A color magazine or "boomerang" consisting of several gel frames which
+can be swung in front of the beam.</t>
+  </si>
+  <si>
+    <t>Boomerang</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - A metal flag used in larger follow spots and projection equipment to cut off the
+light beam without cutting off the electrical supply. Discharge lamps cannot be dimmed,
+so this is the only way of stopping light. Discharge lamps need a period of cooling down
+when they are turned off before they can be turned on again, so they should not be
+switched off if needed again within about two hours.</t>
+  </si>
+  <si>
+    <t>Douser</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Two horizontal masking shutters used in follow spots to shape the
+beam above and below.</t>
+  </si>
+  <si>
+    <t>Gate or Choppers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Adjustable aperture which, when placed in the gate of a profile lantern, varies the
+size of a beam of light. Originally, iris diaphragm. Most follow spots have an iris
+permanently installed.</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Cyc for short. A background device employed to cover the back and
+sometimes the sides of the stage and used with special lighting to create the illusion of
+sky, open space, or great distance at the rear of the stage setting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - To reduce the beam size of a Fresnel by moving the lamp further from the lens.</t>
+  </si>
+  <si>
+    <t>Spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Remotely controllable "intelligent" lighting instrument.
+Each instrument is capable of a massive variety of effects which are operated live via a
+moving light control desk or can be pre-programmed by a standard memory lighting
+desk. The instruments require a power supply and a data cable (normally carrying
+DMX512 signal from the control desk).</t>
+  </si>
+  <si>
+    <t>Moving Head or Moving Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – A metal blade which can be used to shape the edge of the beam of light.
+Shutters (normally four) are located in the gate at the center of the light. The position of
+a shutter in the light beam is known as the shutter cut.</t>
+  </si>
+  <si>
+    <t>Shutters</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - An instrument specially designed for lighting cycloramas. They serve one of
+the same functions as a strip light. Their reflector, however, shapes the field in such a
+way that the cyc is illuminated as brightly at the bottom as it is at the top.  Used often to light a cyclorama, backdrop or background.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - </t>
+  </si>
+  <si>
+    <t>Electrical or electronic device that controls the amount of electricity passed to
+a lamp, and therefore the intensity of the lamp.  A device which regulates the power sent to a lighting instrument (typically incandescent) this allows the intensity of the instrument to be varied. Usually DMX controlled, but could be controlled via an analog or proprietary protocols.</t>
+  </si>
+  <si>
+    <t>A number of individual dimmer circuits mounted in a cabinet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMX (Digital Multiplex) - The standard digital communication protocol that is used to
+remotely control dimmer rack and intelligent lighting fixtures. An industry standard lighting control protocol. A universe is a group of 512 addresses, numbered 1 through 512. See also RDM. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A set of channels, 512 to be precise, on which DMX signals operate.</t>
+  </si>
+  <si>
+    <t>: a coloured sheet of special plastic which is used to physically change the colour of a light. A transparent colored material that is used in theater, event production, photography, videography and cinematography to color light and for color correction.</t>
+  </si>
+  <si>
+    <t>(Parabolic aluminized reflector) - Short for parabolic aluminized reflectors. These
+lights throw a bright hazy beam in the shape of an oval or parabola. The body of a PAR-can is nothing but a
+metal shell for the lamp, which includes a lens and reflector within it. A PAR lamp is a lot
+like a car headlight. By putting different versions of the lamp into the instrument, the
+beam can be wide, medium, narrow, or very narrow. Used often for back light or stage
+wash.</t>
+  </si>
+  <si>
+    <t>A type of lighting instrument with a fixed beam width. Some of them look like paint cans. Generally used for washes.</t>
+  </si>
+  <si>
+    <t>This is a management protocol that can run over the same cables as DMX. It is a bi-directional protocol. It can be used to change the configuration of some lighting fixtures (such as our ETC fixtures) without having physical access to the fixture.</t>
   </si>
 </sst>
 </file>
@@ -654,11 +1049,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:D84" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:D84" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
-    <sortCondition ref="A2:A56"/>
-    <sortCondition ref="B2:B56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:D133" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:D133" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D133">
+    <sortCondition ref="A2:A133"/>
+    <sortCondition ref="B2:B133"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{A991846A-4384-6048-992B-FAECE1424BD1}" name="Topic" dataDxfId="3"/>
@@ -967,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327B4C12-DB51-F04E-97D5-67343BD74C6D}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -991,1028 +1386,1616 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D20" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>255</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>232</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>188</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>206</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>205</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="2" t="s">
-        <v>41</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="1"/>
+        <v>135</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="D33" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="2" t="s">
-        <v>103</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>105</v>
+        <v>237</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="C39" s="1"/>
       <c r="D39" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C41" s="1"/>
       <c r="D41" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C42" s="1"/>
       <c r="D42" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>56</v>
+        <v>192</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>60</v>
+        <v>243</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C45" s="1"/>
       <c r="D45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C46" s="1"/>
       <c r="D46" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>8</v>
+        <v>204</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="2" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>97</v>
+        <v>214</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>9</v>
+        <v>252</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>123</v>
+        <v>253</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="2" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C59" s="1"/>
       <c r="D59" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C60" s="1"/>
       <c r="D60" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C61" s="1"/>
       <c r="D61" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C64" s="1"/>
       <c r="D64" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="153" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="2" t="s">
-        <v>162</v>
+        <v>277</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>165</v>
+        <v>251</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>149</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C78" s="1"/>
       <c r="D78" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="2" t="s">
-        <v>177</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C84" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="D84" s="2" t="s">
-        <v>179</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="D85" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="D86" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C90" s="1"/>
+      <c r="D90" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="1"/>
+      <c r="D91" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="D92" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="D95" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="D97" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C98" s="1"/>
+      <c r="D98" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="D99" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="D100" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="D101" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="D102" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="D103" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="D104" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="D105" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="D106" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="D107" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="D110" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="D113" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="D114" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" s="1"/>
+      <c r="D115" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C116" s="1"/>
+      <c r="D116" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="D119" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" s="1"/>
+      <c r="D120" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="D121" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" s="1"/>
+      <c r="D122" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="D123" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C126" s="1"/>
+      <c r="D126" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C127" s="1"/>
+      <c r="D127" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C128" s="1"/>
+      <c r="D128" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C129" s="1"/>
+      <c r="D129" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C130" s="1"/>
+      <c r="D130" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="1"/>
+      <c r="D132" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" s="1"/>
+      <c r="D133" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/glossary.xlsx
+++ b/glossary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DC177A-AAC5-A246-9E9E-1180E16C9235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A652120-78EB-404A-9808-7207AF54CE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{FD61D8A1-D7A7-6B4D-AB92-59721C5EF8F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="328">
   <si>
     <t>Topic</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Channel</t>
   </si>
   <si>
-    <t xml:space="preserve">: In the context of lighting at UAC, a channel is a configuration item in the colorSource console. It controls one to many DMX addresses. If the console knows what kind of instrument a channel is assigned to, it is automatically configured for the correct behaviours (colour, strobe, etc). </t>
-  </si>
-  <si>
     <t>Dimmer</t>
   </si>
   <si>
@@ -137,9 +134,6 @@
     <t>Rotator</t>
   </si>
   <si>
-    <t xml:space="preserve">: a device which spins a Gobo. Usually Inserted into a lighting instrument where the Gobo holder would go. </t>
-  </si>
-  <si>
     <t>Top Hat</t>
   </si>
   <si>
@@ -206,9 +200,6 @@
     <t>Theme</t>
   </si>
   <si>
-    <t>A *theme* is a predefined design template or style that you can apply to your presentations. It includes elements like fonts, colors, backgrounds, and slide layouts.</t>
-  </si>
-  <si>
     <t>Depth of Field (DoF)</t>
   </si>
   <si>
@@ -312,12 +303,6 @@
   </si>
   <si>
     <t>HDBaseT</t>
-  </si>
-  <si>
-    <t>A electrical protocol for transmitting HD video over *Category Cable*. This is not a network protocol.</t>
-  </si>
-  <si>
-    <t>A general classification of cabling that is often used for networks, but can also be used for video (see *HDBaseT*),* DMX*, or audio. There are several 'categories' in common use, eg cat5e, and cat6.</t>
   </si>
   <si>
     <t>Power</t>
@@ -426,9 +411,6 @@
     <t>Black hinged panels or shutters (which open and close like real barn doors) attached to the front of a lamp fixture to control the spread of the light beam. Also see Snoots (or Snouts) .</t>
   </si>
   <si>
-    <t>Scoop: See Flood,</t>
-  </si>
-  <si>
     <t>Broad</t>
   </si>
   <si>
@@ -463,9 +445,6 @@
   </si>
   <si>
     <t>Flag</t>
-  </si>
-  <si>
-    <t>Small rectangular gobo. An even smaller gobo is termed a clip. Terminology is quite fluid here; a thin flag might be called a blade; a round one might be called a target or (if very small) a dot. A flag with a small hole is called an ear.</t>
   </si>
   <si>
     <t>Flood</t>
@@ -583,19 +562,6 @@
     <t>Distribution</t>
   </si>
   <si>
-    <t xml:space="preserve"> - The use of color is one of the most noticeable defining elements of any lighting
-design. For many designers, color is the most personal of elements, and often times not
-only defines the design, but the personal style of the designer.</t>
-  </si>
-  <si>
-    <t>Color</t>
-  </si>
-  <si>
-    <t>– Any change in visibility, intensity, distribution, or color, as well as physical
-movement when using Moving Lights. Not as apparent as some of the others, this is still
-a very important element that has a significant effect on the lighting design.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Movement </t>
   </si>
   <si>
@@ -634,27 +600,10 @@
     <t>Electromagnetic Spectrum</t>
   </si>
   <si>
-    <t xml:space="preserve"> – Lighting fixture that can be used to create a general "fill" of light and
-color evenly across the stage.</t>
-  </si>
-  <si>
     <t>Wash Fixture</t>
   </si>
   <si>
-    <t xml:space="preserve"> – Fixture with a hard-edged beam. These fixtures are best for creating a
-“special” or using light to mask off a small, precise area, and also are the fixtures to use if
-you want to project a pattern, or “gobo”.</t>
-  </si>
-  <si>
     <t>Spot Fixture</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - The most commonly known instrument. Follow spots are used to highlight
-and follow a single performer onstage. Spotlights are controlled by a spotlight operator
-(or Spot Op) who tracks actors around the stage. Follow spots require a certain amount
-of skill to operate smoothly. They typically have a variety of colors that can be inserted
-with the flip of a lever, as well as a gate, dowser, focus control, and an iris. Used to
-follow a lead talent on stage.</t>
   </si>
   <si>
     <t>Follow Spot</t>
@@ -731,12 +680,6 @@
   </si>
   <si>
     <t>Four Point Lighting</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> – This method is widely known and used by theatre professionals.
-It uses two front lights at a 45-degree angle of the subject, one side being a warm gel
-color and the other side being a cool gel color. This helps replicate a highlight and
-shadow contrast with lighting.</t>
   </si>
   <si>
     <t>McCandless Method</t>
@@ -874,10 +817,6 @@
     <t>Gobo or Template</t>
   </si>
   <si>
-    <t xml:space="preserve"> - A color magazine or "boomerang" consisting of several gel frames which
-can be swung in front of the beam.</t>
-  </si>
-  <si>
     <t>Boomerang</t>
   </si>
   <si>
@@ -943,21 +882,7 @@
     <t xml:space="preserve"> - </t>
   </si>
   <si>
-    <t>Electrical or electronic device that controls the amount of electricity passed to
-a lamp, and therefore the intensity of the lamp.  A device which regulates the power sent to a lighting instrument (typically incandescent) this allows the intensity of the instrument to be varied. Usually DMX controlled, but could be controlled via an analog or proprietary protocols.</t>
-  </si>
-  <si>
     <t>A number of individual dimmer circuits mounted in a cabinet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMX (Digital Multiplex) - The standard digital communication protocol that is used to
-remotely control dimmer rack and intelligent lighting fixtures. An industry standard lighting control protocol. A universe is a group of 512 addresses, numbered 1 through 512. See also RDM. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A set of channels, 512 to be precise, on which DMX signals operate.</t>
-  </si>
-  <si>
-    <t>: a coloured sheet of special plastic which is used to physically change the colour of a light. A transparent colored material that is used in theater, event production, photography, videography and cinematography to color light and for color correction.</t>
   </si>
   <si>
     <t>(Parabolic aluminized reflector) - Short for parabolic aluminized reflectors. These
@@ -971,7 +896,229 @@
     <t>A type of lighting instrument with a fixed beam width. Some of them look like paint cans. Generally used for washes.</t>
   </si>
   <si>
-    <t>This is a management protocol that can run over the same cables as DMX. It is a bi-directional protocol. It can be used to change the configuration of some lighting fixtures (such as our ETC fixtures) without having physical access to the fixture.</t>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>A proprietary protocol fo Audiante, but widely used in the industry. It is most known for its ability to transpot high quality audio over an IP network. It can also handle video.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - A colour magazine or "boomerang" consisting of several gel frames which
+can be swung in front of the beam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">: In the context of lighting at UAC, a channel is a configuration item in the colourSource console. It controls one to many DMX addresses. If the console knows what kind of instrument a channel is assigned to, it is automatically configured for the correct behaviours (colour, strobe, etc). </t>
+  </si>
+  <si>
+    <t>colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The use of colour is one of the most noticeable defining elements of any lighting
+design. For many designers, colour is the most personal of elements, and often times not
+only defines the design, but the personal style of the designer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - The most commonly known instrument. Follow spots are used to highlight
+and follow a single performer onstage. Spotlights are controlled by a spotlight operator
+(or Spot Op) who tracks actors around the stage. Follow spots require a certain amount
+of skill to operate smoothly. They typically have a variety of colours that can be inserted
+with the flip of a lever, as well as a gate, dowser, focus control, and an iris. Used to
+follow a lead talent on stage.</t>
+  </si>
+  <si>
+    <t>: a coloured sheet of special plastic which is used to physically change the colour of a light. A transparent coloured material that is used in theater, event production, photography, videography and cinematography to colour light and for colour correction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – This method is widely known and used by theatre professionals.
+It uses two front lights at a 45-degree angle of the subject, one side being a warm gel
+colour and the other side being a cool gel colour. This helps replicate a highlight and
+shadow contrast with lighting.</t>
+  </si>
+  <si>
+    <t>– Any change in visibility, intensity, distribution, or colour, as well as physical
+movement when using Moving Lights. Not as apparent as some of the others, this is still
+a very important element that has a significant effect on the lighting design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Lighting fixture that can be used to create a general "fill" of light and
+colour evenly across the stage.</t>
+  </si>
+  <si>
+    <t>A *theme* is a predefined design template or style that you can apply to your presentations. It includes elements like fonts, colours, backgrounds, and slide layouts.</t>
+  </si>
+  <si>
+    <t>SDI, NDI</t>
+  </si>
+  <si>
+    <t>SDI, HDBaseT</t>
+  </si>
+  <si>
+    <t>NDI, HDBaseT</t>
+  </si>
+  <si>
+    <t>A electrical protocol for transmitting HD video over *Category Cable*. This is not a network protocol. See https://en.wikipedia.org/wiki/HDBaseT</t>
+  </si>
+  <si>
+    <t>XLR</t>
+  </si>
+  <si>
+    <t>RJ45</t>
+  </si>
+  <si>
+    <t>8P8C</t>
+  </si>
+  <si>
+    <t>A type of locking connector common in the AV field. They come in a variety of pin counts. 3-pin is used for audio (mic cables) and also some lighting [[DMX]] cables (but the cable is different). 4-pin is used for comminication headsets and for some lighting applications (such as rotators). 5-pin is used for lighting [[DMX]] cables. See https://en.wikipedia.org/wiki/XLR_connector</t>
+  </si>
+  <si>
+    <t>The 8P8C connector is commonly used for Ethernet and [[HDBaseT]], and sometimes for [[DMX]]. See https://en.wikipedia.org/wiki/Modular_connector#8P8C</t>
+  </si>
+  <si>
+    <t>A common name for the [[8P8C]] connector commonly used for [[Ethernet]] and [[HDBaseT]]. See https://en.wikipedia.org/wiki/Modular_connector#8P8C</t>
+  </si>
+  <si>
+    <t>A general classification of cabling that is often used for networks, but can also be used for video (see [[HDBaseT]]), [[DMX]], or audio. There are several 'categories' in common use, eg cat5e, and cat6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> – Fixture with a hard-edged beam. These fixtures are best for creating a
+“special” or using light to mask off a small, precise area, and also are the fixtures to use if
+you want to project a pattern, or “[[gobo]]”.</t>
+  </si>
+  <si>
+    <t>Scoop: See [[Flood]].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">: a device which spins a [[Gobo]]. Usually Inserted into a lighting instrument where the [[Gobo]] holder would go. </t>
+  </si>
+  <si>
+    <t>This is a management protocol that can run over the same cables as [[DMX]]. It is a bi-directional protocol. It can be used to change the configuration of some lighting fixtures (such as our ETC fixtures) without having physical access to the fixture.</t>
+  </si>
+  <si>
+    <t>Small rectangular gobo. An even smaller [[gobo]] is termed a clip. Terminology is quite fluid here; a thin flag might be called a blade; a round one might be called a target or (if very small) a dot. A flag with a small hole is called an ear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A set of channels, 512 to be precise, on which [[DMX]] signals operate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMX (Digital Multiplex) - The standard digital communication protocol that is used to
+remotely control dimmer rack and intelligent lighting fixtures. An industry standard lighting control protocol. A universe is a group of 512 addresses, numbered 1 through 512. See also [[RDM]]. </t>
+  </si>
+  <si>
+    <t>Electrical or electronic device that controls the amount of electricity passed to
+a lamp, and therefore the intensity of the lamp.  A device which regulates the power sent to a lighting instrument (typically incandescent) this allows the intensity of the instrument to be varied. Usually [[DMX]] controlled, but could be controlled via an analog or proprietary protocols.</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>A controllable parameter of a [[Fixture]] in grandMA3 (e.g. Dimmer, Pan, Tilt, Color, Beam), organised into Feature Groups within the Patch &amp; Fixture Schedule.</t>
+  </si>
+  <si>
+    <t>A snapshot of lighting output stored inside a [[Sequence]] in grandMA3, capturing [[Attribute]] values and timing information for one moment in a show.</t>
+  </si>
+  <si>
+    <t>Digital Multiplex; the serial control protocol grandMA3 uses to send 512 channel values per [[Universe]] to dimmers and [[Fixture]]s, delivered via XLR cable or through a [[Network Node]].</t>
+  </si>
+  <si>
+    <t>Executor</t>
+  </si>
+  <si>
+    <t>A physical fader, button pair, or on-screen control on the grandMA3 surface assigned to play back a [[Sequence]], [[Preset]], or other pool object.</t>
+  </si>
+  <si>
+    <t>Fixture</t>
+  </si>
+  <si>
+    <t>A programmable lighting device patched into grandMA3 via the Patch &amp; Fixture Schedule, represented as an object whose [[Attribute]]s are controlled by the console.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>A named, stored selection of [[Fixture]]s in the grandMA3 Group pool, recalled to quickly select multiple fixtures for programming without re-selecting them individually.</t>
+  </si>
+  <si>
+    <t>Layout</t>
+  </si>
+  <si>
+    <t>A grandMA3 view that arranges [[Fixture]] icons on a custom 2D canvas, providing a visual stage map for intuitive selection and real-time feedback during programming.</t>
+  </si>
+  <si>
+    <t>MA-Net3</t>
+  </si>
+  <si>
+    <t>The proprietary high-speed Ethernet protocol grandMA3 uses to distribute lighting data between the console, [[Network Node]]s, [[onPC]] sessions, and other MA3 devices.</t>
+  </si>
+  <si>
+    <t>MAtricks</t>
+  </si>
+  <si>
+    <t>The grandMA3 built-in tool for distributing [[Attribute]] values mathematically across a [[Fixture]] selection, enabling fans, waves, grids, and other pattern-based programming without manual entry.</t>
+  </si>
+  <si>
+    <t>Network Node</t>
+  </si>
+  <si>
+    <t>A grandMA3 hardware device (e.g. grandMA3 Node 4) that receives data via [[MA-Net3]] and converts it to physical DMX outputs, extending the console's universe count over Ethernet.</t>
+  </si>
+  <si>
+    <t>onPC</t>
+  </si>
+  <si>
+    <t>The grandMA3 software application that runs the full MA3 operating system on a Windows PC, enabling programming and show playback without dedicated grandMA3 console hardware.</t>
+  </si>
+  <si>
+    <t>Phaser</t>
+  </si>
+  <si>
+    <t>A grandMA3 object that drives cyclic time-based variations across [[Attribute]]s of selected [[Fixture]]s, replacing the Effects engine from earlier MA console generations.</t>
+  </si>
+  <si>
+    <t>Plugin</t>
+  </si>
+  <si>
+    <t>A user-created script written in Lua and stored in the grandMA3 Plugin pool, used to automate repetitive tasks or extend console functionality beyond built-in features.</t>
+  </si>
+  <si>
+    <t>Preset</t>
+  </si>
+  <si>
+    <t>A named set of [[Attribute]] values for one or more [[Fixture]]s stored in the grandMA3 Preset pool; [[Cue]]s that reference a preset update automatically when the preset is edited.</t>
+  </si>
+  <si>
+    <t>Programmer</t>
+  </si>
+  <si>
+    <t>The temporary workspace in grandMA3 where [[Attribute]] values are adjusted before being stored into a [[Cue]] or [[Preset]]; programmer values take priority over all active [[Sequence]] output.</t>
+  </si>
+  <si>
+    <t>Sequence</t>
+  </si>
+  <si>
+    <t>The primary playback object in grandMA3; a container of [[Cue]]s that executes in order or via user-defined cue links, and is assigned to an [[Executor]] for live control.</t>
+  </si>
+  <si>
+    <t>SpeedMaster</t>
+  </si>
+  <si>
+    <t>A grandMA3 pool object assigned to an [[Executor]] that controls the playback rate of [[Phaser]]s or [[Sequence]] timing linked to it, enabling real-time tempo adjustment during a show.</t>
+  </si>
+  <si>
+    <t>Timecode</t>
+  </si>
+  <si>
+    <t>An external time-reference signal (e.g. SMPTE LTC, MIDI Timecode) that grandMA3 can receive to trigger [[Cue]]s or drive [[Executor]]s at frame-accurate timestamps.</t>
+  </si>
+  <si>
+    <t>Universe</t>
+  </si>
+  <si>
+    <t>A single DMX data stream in grandMA3 containing 512 individually addressed channels, assigned to physical XLR ports or [[Network Node]] outputs via the grandMA3 Patch.</t>
+  </si>
+  <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>A grandMA3 object that defines a named subset of patched [[Fixture]]s accessible to a specific user or station, enabling multi-user show file collaboration without fixture conflicts.</t>
   </si>
 </sst>
 </file>
@@ -1049,8 +1196,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:D133" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:D133" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:D157" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:D157" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D133">
     <sortCondition ref="A2:A133"/>
     <sortCondition ref="B2:B133"/>
@@ -1362,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327B4C12-DB51-F04E-97D5-67343BD74C6D}">
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -1386,1409 +1533,1411 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
-        <v>19</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="2" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="2" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="2" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="2" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="2" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="2" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="2" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="2" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="2" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="2" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="2" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C66" s="1"/>
+        <v>145</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>229</v>
+      </c>
       <c r="D66" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="153" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="2" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="2" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="2" t="s">
-        <v>181</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="2" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="2" t="s">
-        <v>33</v>
+        <v>284</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="2" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2" t="s">
-        <v>195</v>
+        <v>282</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="2" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="2" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="2" t="s">
-        <v>93</v>
+        <v>281</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C111" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>4</v>
@@ -2802,7 +2951,7 @@
     </row>
     <row r="118" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>5</v>
@@ -2816,14 +2965,14 @@
     </row>
     <row r="119" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="2" t="s">
-        <v>56</v>
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="51" x14ac:dyDescent="0.2">
@@ -2843,11 +2992,11 @@
         <v>14</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -2867,11 +3016,11 @@
         <v>14</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -2891,25 +3040,27 @@
         <v>14</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C126" s="1"/>
+        <v>88</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="D126" s="2" t="s">
-        <v>92</v>
+        <v>274</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2917,11 +3068,13 @@
         <v>14</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C127" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="D127" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -2929,11 +3082,11 @@
         <v>14</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2941,11 +3094,13 @@
         <v>14</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C129" s="1"/>
+        <v>99</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="D129" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -2953,11 +3108,11 @@
         <v>14</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="85" x14ac:dyDescent="0.2">
@@ -2965,13 +3120,13 @@
         <v>14</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2995,7 +3150,299 @@
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C135" s="1"/>
+      <c r="D135" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="1"/>
+      <c r="D137" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/glossary.xlsx
+++ b/glossary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3B644F-109A-DD44-B5E3-DADBE89512D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105215B6-4183-FA44-891E-21F40F93D067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{FD61D8A1-D7A7-6B4D-AB92-59721C5EF8F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="333">
   <si>
     <t>Topic</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>This is a heavy duty 20 Amp  connector with circular locking contacts  (hence the **L** in the name). There is an *R* and a *P* suffix for the *recepacle* and *plug*.</t>
-  </si>
-  <si>
-    <t>This is a regular three-prong   connector  good for 15 Amps . There is an *R* and a *P* suffix for the *recepacle* and *plug*.</t>
   </si>
   <si>
     <t>Nema 5-15</t>
@@ -1119,6 +1116,24 @@
 The base of the yoke is typically a single bolt around which the yoke can be rotated,
 providing a second axis of rotation. Combined together, these two axes allow the fixture
 to point nearly anywhere in a spherical range of motion encircling the yoke.</t>
+  </si>
+  <si>
+    <t>Nema 1-15</t>
+  </si>
+  <si>
+    <t>This is a regular two-prong  connector good for 15 Amps . There is an *R* and a *P* suffix for the *recepacle* and *plug*.</t>
+  </si>
+  <si>
+    <t>This is a regular three-prong connector good for 15 Amps . There is an *R* and a *P* suffix for the *recepacle* and *plug*.</t>
+  </si>
+  <si>
+    <t>Nema 5-15, Nema 6-20</t>
+  </si>
+  <si>
+    <t>Nema 1-15, Nema 6-20</t>
+  </si>
+  <si>
+    <t>Nema 1-15, Nema 5-15</t>
   </si>
 </sst>
 </file>
@@ -1168,13 +1183,13 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1199,17 +1214,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:E158" totalsRowShown="0" dataDxfId="5">
-  <autoFilter ref="A1:E158" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E158">
-    <sortCondition ref="B1:B158"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:E159" totalsRowShown="0" dataDxfId="5">
+  <autoFilter ref="A1:E159" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E159">
+    <sortCondition ref="B1:B159"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A991846A-4384-6048-992B-FAECE1424BD1}" name="Topic" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{ABA7B585-B679-4046-A73C-5497CC96B4A8}" name="Term" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{BCC184D7-6C8F-B940-B216-AB00E086E8CE}" name="Sense" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{01E09C02-E371-8D42-9078-8A75C09E6982}" name="SeeAlso" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{A2D271FE-F834-0142-AB0D-F732DE4B8C76}" name="Definition" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{BCC184D7-6C8F-B940-B216-AB00E086E8CE}" name="Sense" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{01E09C02-E371-8D42-9078-8A75C09E6982}" name="SeeAlso" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{A2D271FE-F834-0142-AB0D-F732DE4B8C76}" name="Definition" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1512,11 +1527,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327B4C12-DB51-F04E-97D5-67343BD74C6D}">
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="94.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1529,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1543,14 +1558,14 @@
         <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -1558,14 +1573,14 @@
         <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1603,14 +1618,14 @@
         <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1618,14 +1633,14 @@
         <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -1633,14 +1648,14 @@
         <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1648,16 +1663,16 @@
         <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1665,14 +1680,14 @@
         <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1680,14 +1695,14 @@
         <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1695,14 +1710,14 @@
         <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1710,14 +1725,14 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1755,14 +1770,14 @@
         <v>82</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1777,7 +1792,7 @@
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1785,14 +1800,14 @@
         <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -1800,14 +1815,14 @@
         <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1821,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>57</v>
@@ -1839,7 +1854,7 @@
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1847,14 +1862,14 @@
         <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -1862,14 +1877,14 @@
         <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -1892,14 +1907,14 @@
         <v>28</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -1907,14 +1922,14 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1922,14 +1937,14 @@
         <v>28</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C27" s="1">
         <v>2</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -1937,14 +1952,14 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -1952,14 +1967,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -1967,7 +1982,7 @@
         <v>54</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -1976,7 +1991,7 @@
         <v>76</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2016,16 +2031,16 @@
         <v>28</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -2040,7 +2055,7 @@
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2048,14 +2063,14 @@
         <v>28</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2063,14 +2078,14 @@
         <v>28</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C36" s="1">
         <v>1</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2078,14 +2093,14 @@
         <v>28</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C37" s="1">
         <v>1</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -2108,14 +2123,14 @@
         <v>28</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C39" s="1">
         <v>1</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2123,14 +2138,16 @@
         <v>28</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C40" s="1">
         <v>1</v>
       </c>
-      <c r="D40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="E40" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -2138,14 +2155,14 @@
         <v>28</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C41" s="1">
         <v>2</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2153,14 +2170,14 @@
         <v>28</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="85" x14ac:dyDescent="0.2">
@@ -2168,14 +2185,14 @@
         <v>28</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2198,16 +2215,16 @@
         <v>14</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2215,14 +2232,14 @@
         <v>28</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2230,14 +2247,14 @@
         <v>28</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C47" s="1">
         <v>1</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="85" x14ac:dyDescent="0.2">
@@ -2245,14 +2262,14 @@
         <v>28</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2277,14 +2294,14 @@
         <v>28</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C50" s="1">
         <v>1</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -2292,14 +2309,14 @@
         <v>28</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C51" s="1">
         <v>1</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2307,14 +2324,14 @@
         <v>28</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C52" s="1">
         <v>1</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2322,14 +2339,14 @@
         <v>28</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2337,14 +2354,14 @@
         <v>28</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C54" s="1">
         <v>1</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2367,14 +2384,14 @@
         <v>28</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2382,14 +2399,14 @@
         <v>28</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C57" s="1">
         <v>1</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="102" x14ac:dyDescent="0.2">
@@ -2397,14 +2414,14 @@
         <v>28</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C58" s="1">
         <v>1</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2412,14 +2429,14 @@
         <v>28</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2449,7 +2466,7 @@
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2464,7 +2481,7 @@
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2479,7 +2496,7 @@
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2494,7 +2511,7 @@
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2502,7 +2519,7 @@
         <v>28</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C65" s="1">
         <v>1</v>
@@ -2511,7 +2528,7 @@
         <v>22</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -2519,14 +2536,14 @@
         <v>28</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C66" s="1">
         <v>1</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2540,10 +2557,10 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2551,16 +2568,16 @@
         <v>82</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C68" s="1">
-        <v>1</v>
-      </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2568,16 +2585,16 @@
         <v>82</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2592,7 +2609,7 @@
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2600,14 +2617,14 @@
         <v>28</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C71" s="1">
         <v>1</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2615,14 +2632,14 @@
         <v>28</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C72" s="1">
         <v>1</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2630,14 +2647,14 @@
         <v>28</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C73" s="1">
         <v>1</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2645,14 +2662,14 @@
         <v>28</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2660,14 +2677,14 @@
         <v>28</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2675,14 +2692,14 @@
         <v>28</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2702,7 +2719,7 @@
     </row>
     <row r="78" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>42</v>
@@ -2720,14 +2737,14 @@
         <v>28</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C79" s="1">
         <v>1</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2742,7 +2759,7 @@
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2750,16 +2767,16 @@
         <v>28</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2767,14 +2784,14 @@
         <v>28</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C82" s="1">
         <v>1</v>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2782,14 +2799,14 @@
         <v>28</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C83" s="1">
         <v>1</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="153" x14ac:dyDescent="0.2">
@@ -2797,19 +2814,19 @@
         <v>28</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C84" s="1">
         <v>1</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>46</v>
@@ -2827,14 +2844,14 @@
         <v>28</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C86" s="1">
         <v>1</v>
       </c>
       <c r="D86" s="1"/>
       <c r="E86" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -2842,14 +2859,14 @@
         <v>28</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -2857,14 +2874,14 @@
         <v>28</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
       </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -2872,14 +2889,14 @@
         <v>28</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C89" s="1">
         <v>1</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -2887,14 +2904,14 @@
         <v>28</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C90" s="1">
         <v>1</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="85" x14ac:dyDescent="0.2">
@@ -2902,14 +2919,14 @@
         <v>28</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C91" s="1">
         <v>1</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2917,16 +2934,16 @@
         <v>28</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -2940,7 +2957,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>78</v>
@@ -2951,14 +2968,16 @@
         <v>84</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>87</v>
+        <v>327</v>
       </c>
       <c r="C94" s="1">
         <v>1</v>
       </c>
-      <c r="D94" s="1"/>
+      <c r="D94" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="E94" s="2" t="s">
-        <v>86</v>
+        <v>328</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -2966,44 +2985,48 @@
         <v>84</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
       </c>
-      <c r="D95" s="1"/>
+      <c r="D95" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="E95" s="2" t="s">
-        <v>89</v>
+        <v>329</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C96" s="1">
+        <v>1</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C96" s="1">
-        <v>1</v>
-      </c>
-      <c r="D96" s="1"/>
-      <c r="E96" s="2" t="s">
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="1"/>
+      <c r="E97" s="2" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -3011,187 +3034,187 @@
         <v>28</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C98" s="1">
         <v>1</v>
       </c>
       <c r="D98" s="1"/>
       <c r="E98" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="1">
-        <v>1</v>
-      </c>
-      <c r="D99" s="1" t="s">
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E100" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="102" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-      <c r="D100" s="1"/>
-      <c r="E100" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
       </c>
       <c r="D101" s="1"/>
       <c r="E101" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1</v>
+      </c>
+      <c r="D102" s="1"/>
+      <c r="E102" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1</v>
+      </c>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C102" s="1">
-        <v>1</v>
-      </c>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1" t="s">
+    </row>
+    <row r="104" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1</v>
+      </c>
+      <c r="D104" s="1"/>
+      <c r="E104" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A103" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C103" s="1">
-        <v>1</v>
-      </c>
-      <c r="D103" s="1"/>
-      <c r="E103" s="2" t="s">
+      <c r="C105" s="1">
+        <v>1</v>
+      </c>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C107" s="1">
+        <v>1</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1</v>
+      </c>
+      <c r="D109" s="1"/>
+      <c r="E109" s="2" t="s">
         <v>312</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C104" s="1">
-        <v>1</v>
-      </c>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C105" s="1">
-        <v>1</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C106" s="1">
-        <v>1</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C107" s="1">
-        <v>1</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="68" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C108" s="1">
-        <v>1</v>
-      </c>
-      <c r="D108" s="1"/>
-      <c r="E108" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C109" s="1">
-        <v>1</v>
-      </c>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -3199,29 +3222,29 @@
         <v>28</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="C111" s="1">
         <v>1</v>
       </c>
       <c r="D111" s="1"/>
-      <c r="E111" s="2" t="s">
-        <v>270</v>
+      <c r="E111" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -3229,121 +3252,123 @@
         <v>28</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
       </c>
-      <c r="D112" s="1"/>
+      <c r="D112" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="E112" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>217</v>
-      </c>
+      <c r="D114" s="1"/>
       <c r="E114" s="2" t="s">
-        <v>220</v>
+        <v>144</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
       </c>
-      <c r="D115" s="1"/>
+      <c r="D115" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="E115" s="2" t="s">
-        <v>314</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="C116" s="1">
         <v>1</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="C117" s="1">
         <v>1</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C118" s="1">
+        <v>1</v>
+      </c>
+      <c r="D118" s="1"/>
+      <c r="E118" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C118" s="1">
-        <v>1</v>
-      </c>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1" t="s">
+      <c r="C119" s="1">
+        <v>1</v>
+      </c>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C119" s="1">
-        <v>1</v>
-      </c>
-      <c r="D119" s="1"/>
-      <c r="E119" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -3351,125 +3376,125 @@
         <v>28</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="C120" s="1">
         <v>1</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="D120" s="1"/>
       <c r="E120" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C121" s="1">
+        <v>1</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C121" s="1">
-        <v>1</v>
-      </c>
-      <c r="D121" s="1" t="s">
+      <c r="C122" s="1">
+        <v>1</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C122" s="1">
-        <v>1</v>
-      </c>
-      <c r="D122" s="1"/>
-      <c r="E122" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C123" s="1">
+        <v>1</v>
+      </c>
+      <c r="D123" s="1"/>
+      <c r="E123" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B124" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C124" s="1">
+        <v>1</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C123" s="1">
-        <v>1</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B124" s="1" t="s">
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C125" s="1">
+        <v>1</v>
+      </c>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C124" s="1">
-        <v>1</v>
-      </c>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C125" s="1">
-        <v>1</v>
-      </c>
-      <c r="D125" s="1"/>
-      <c r="E125" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="C126" s="1">
         <v>1</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="C127" s="1">
         <v>1</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="2" t="s">
-        <v>148</v>
+        <v>316</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -3477,59 +3502,59 @@
         <v>28</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="C128" s="1">
         <v>1</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C129" s="1">
+        <v>1</v>
+      </c>
+      <c r="D129" s="1"/>
+      <c r="E129" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C130" s="1">
+        <v>1</v>
+      </c>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C129" s="1">
-        <v>1</v>
-      </c>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A130" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C130" s="1">
-        <v>1</v>
-      </c>
-      <c r="D130" s="1"/>
-      <c r="E130" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C131" s="1">
         <v>1</v>
       </c>
       <c r="D131" s="1"/>
       <c r="E131" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -3537,269 +3562,269 @@
         <v>28</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="C132" s="1">
         <v>1</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="C133" s="1">
         <v>1</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C134" s="1">
         <v>1</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="2" t="s">
-        <v>154</v>
+        <v>319</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="C135" s="1">
         <v>1</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>183</v>
+        <v>30</v>
       </c>
       <c r="C136" s="1">
         <v>1</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="C137" s="1">
         <v>1</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="C138" s="1">
         <v>1</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C139" s="1">
         <v>1</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C140" s="1">
+        <v>1</v>
+      </c>
+      <c r="D140" s="1"/>
+      <c r="E140" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C140" s="1">
-        <v>1</v>
-      </c>
-      <c r="D140" s="1"/>
-      <c r="E140" s="2"/>
-    </row>
-    <row r="141" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A141" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="B141" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1</v>
+      </c>
+      <c r="D141" s="1"/>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1</v>
+      </c>
+      <c r="D142" s="1"/>
+      <c r="E142" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C141" s="1">
-        <v>1</v>
-      </c>
-      <c r="D141" s="1"/>
-      <c r="E141" s="2" t="s">
+    </row>
+    <row r="143" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C143" s="1">
+        <v>1</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="85" x14ac:dyDescent="0.2">
-      <c r="A142" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C142" s="1">
-        <v>1</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A143" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C143" s="1">
-        <v>1</v>
-      </c>
-      <c r="D143" s="1"/>
-      <c r="E143" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A144" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C144" s="1">
         <v>1</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="2" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="C145" s="1">
         <v>1</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="C146" s="1">
         <v>1</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="2" t="s">
-        <v>40</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C147" s="1">
         <v>1</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1</v>
+      </c>
+      <c r="D148" s="1"/>
+      <c r="E148" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B148" s="1" t="s">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1</v>
+      </c>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="C148" s="1">
-        <v>1</v>
-      </c>
-      <c r="D148" s="1"/>
-      <c r="E148" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A149" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C149" s="1">
-        <v>1</v>
-      </c>
-      <c r="D149" s="1"/>
-      <c r="E149" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -3807,135 +3832,150 @@
         <v>28</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="C150" s="1">
         <v>1</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C151" s="1">
+        <v>1</v>
+      </c>
+      <c r="D151" s="1"/>
+      <c r="E151" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C151" s="1">
-        <v>1</v>
-      </c>
-      <c r="D151" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E151" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1">
+        <v>1</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C153" s="1">
+        <v>1</v>
+      </c>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C152" s="1">
-        <v>1</v>
-      </c>
-      <c r="D152" s="1"/>
-      <c r="E152" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="85" x14ac:dyDescent="0.2">
-      <c r="A153" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C153" s="1">
-        <v>1</v>
-      </c>
-      <c r="D153" s="1"/>
-      <c r="E153" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C154" s="1">
         <v>1</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B155" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1</v>
+      </c>
+      <c r="D155" s="1"/>
+      <c r="E155" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1</v>
+      </c>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="C155" s="1">
-        <v>1</v>
-      </c>
-      <c r="D155" s="1"/>
-      <c r="E155" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" ht="68" x14ac:dyDescent="0.2">
-      <c r="A156" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C156" s="1">
-        <v>1</v>
-      </c>
-      <c r="D156" s="1"/>
-      <c r="E156" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C157" s="1">
         <v>1</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>10</v>
+        <v>196</v>
       </c>
       <c r="C158" s="1">
         <v>1</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1</v>
+      </c>
+      <c r="D159" s="1"/>
+      <c r="E159" s="2" t="s">
         <v>43</v>
       </c>
     </row>
